--- a/data/trans_orig/IP40-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP40-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según como llegan a fin de mes con los ingresos de su hogar en 2012 (tasa de respuesta: 97,0%)</t>
+          <t>Adultos según como llegan a fin de mes con los ingresos de su hogar en 2012 (tasa de respuesta: 97,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8785</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2374</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10013</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10608</t>
+          <t>10398</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22315</t>
+          <t>22425</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19968</t>
+          <t>18945</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19996</t>
+          <t>20735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36983</t>
+          <t>37188</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22721</t>
+          <t>22608</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38078</t>
+          <t>38071</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18888</t>
+          <t>19198</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32414</t>
+          <t>32875</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45975</t>
+          <t>45031</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65624</t>
+          <t>65221</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,35%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27398</t>
+          <t>27103</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>14823</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27652</t>
+          <t>27466</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32299</t>
+          <t>31755</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51155</t>
+          <t>50470</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17231</t>
+          <t>17598</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30696</t>
+          <t>31155</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15550</t>
+          <t>15565</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>28288</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>36686</t>
+          <t>35801</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>55817</t>
+          <t>54967</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9735</t>
+          <t>9374</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23663</t>
+          <t>23396</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41022</t>
+          <t>40675</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32824</t>
+          <t>33111</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54310</t>
+          <t>54540</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>61253</t>
+          <t>61448</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>89535</t>
+          <t>89835</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74177</t>
+          <t>73312</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101529</t>
+          <t>101354</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74395</t>
+          <t>74339</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102913</t>
+          <t>101278</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>154737</t>
+          <t>155470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>194413</t>
+          <t>193830</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>133919</t>
+          <t>132565</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>165979</t>
+          <t>165088</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137147</t>
+          <t>136176</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170861</t>
+          <t>169487</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>279284</t>
+          <t>278572</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>326793</t>
+          <t>326658</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,82%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87706</t>
+          <t>87074</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>117224</t>
+          <t>115713</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>86808</t>
+          <t>85588</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>116256</t>
+          <t>117233</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>184973</t>
+          <t>183570</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>224749</t>
+          <t>223784</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57605</t>
+          <t>57823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82995</t>
+          <t>82898</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72389</t>
+          <t>71461</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98599</t>
+          <t>99639</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>137665</t>
+          <t>135974</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>173075</t>
+          <t>173227</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,0%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11794</t>
+          <t>11250</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7723</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14652</t>
+          <t>15207</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30698</t>
+          <t>30862</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49296</t>
+          <t>49939</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34818</t>
+          <t>35551</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54521</t>
+          <t>54377</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70799</t>
+          <t>71006</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>96979</t>
+          <t>97945</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41566</t>
+          <t>41075</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61181</t>
+          <t>60987</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48617</t>
+          <t>48074</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68272</t>
+          <t>68936</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94703</t>
+          <t>95615</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>123538</t>
+          <t>123451</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32729</t>
+          <t>32279</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51507</t>
+          <t>50266</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32417</t>
+          <t>31925</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50243</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>70431</t>
+          <t>70556</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>96511</t>
+          <t>96732</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14224</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27239</t>
+          <t>27638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>11163</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23728</t>
+          <t>23773</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28428</t>
+          <t>28888</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46609</t>
+          <t>47238</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>9721</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14583</t>
+          <t>14581</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20095</t>
+          <t>21346</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>12573</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12396</t>
+          <t>12317</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21268</t>
+          <t>20475</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>59868</t>
+          <t>59835</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>88874</t>
+          <t>86560</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>77275</t>
+          <t>74143</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>107287</t>
+          <t>105894</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>144209</t>
+          <t>145081</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>183940</t>
+          <t>186155</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>135553</t>
+          <t>136507</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>173318</t>
+          <t>168659</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>140035</t>
+          <t>140823</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>175787</t>
+          <t>176696</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>285346</t>
+          <t>284222</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>339141</t>
+          <t>336993</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>200067</t>
+          <t>200493</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>239366</t>
+          <t>239882</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>200237</t>
+          <t>198853</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>239256</t>
+          <t>238985</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>411775</t>
+          <t>415270</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>472401</t>
+          <t>470324</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>124938</t>
+          <t>127095</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>160360</t>
+          <t>159388</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>122885</t>
+          <t>122077</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>156098</t>
+          <t>157367</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>256226</t>
+          <t>257043</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>306287</t>
+          <t>306522</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>85238</t>
+          <t>83187</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>116007</t>
+          <t>111461</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>100926</t>
+          <t>98665</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>131478</t>
+          <t>131459</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>188825</t>
+          <t>188129</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>233936</t>
+          <t>233987</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según como llegan a fin de mes con los ingresos de su hogar en 2016 (tasa de respuesta: 98,82%)</t>
+          <t>Adultos según como llegan a fin de mes con los ingresos de su hogar en 2016 (tasa de respuesta: 98,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -4291,12 +4291,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>731</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>894</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -4369,12 +4369,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>782</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11381</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -4482,12 +4482,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>15226</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8899</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19798</t>
+          <t>20360</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17064</t>
+          <t>16831</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32145</t>
+          <t>31080</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -4595,12 +4595,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>13930</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25258</t>
+          <t>25078</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4610,12 +4610,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16936</t>
+          <t>17328</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29793</t>
+          <t>30147</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33335</t>
+          <t>32879</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51498</t>
+          <t>51318</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,13%</t>
         </is>
       </c>
     </row>
@@ -4708,12 +4708,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18989</t>
+          <t>18953</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32094</t>
+          <t>30873</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4723,12 +4723,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18607</t>
+          <t>18648</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31609</t>
+          <t>31757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4758,12 +4758,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39540</t>
+          <t>41359</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>58279</t>
+          <t>59582</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>562</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23411</t>
+          <t>23712</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40696</t>
+          <t>41897</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30019</t>
+          <t>29560</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>50609</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57802</t>
+          <t>57872</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83885</t>
+          <t>84235</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5164,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84302</t>
+          <t>84750</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111706</t>
+          <t>112125</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69650</t>
+          <t>69708</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95881</t>
+          <t>96410</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>162519</t>
+          <t>161012</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>199841</t>
+          <t>199313</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -5277,12 +5277,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>128313</t>
+          <t>127914</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160275</t>
+          <t>160508</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>128920</t>
+          <t>129719</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>162830</t>
+          <t>163204</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>269990</t>
+          <t>268409</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>316873</t>
+          <t>316055</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,28%</t>
         </is>
       </c>
     </row>
@@ -5390,12 +5390,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93544</t>
+          <t>93768</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>124181</t>
+          <t>124038</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>120140</t>
+          <t>119600</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>151697</t>
+          <t>152151</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>222210</t>
+          <t>220537</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>266759</t>
+          <t>265321</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -5503,12 +5503,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70677</t>
+          <t>72086</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98454</t>
+          <t>98718</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>68520</t>
+          <t>66829</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95193</t>
+          <t>94672</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>146325</t>
+          <t>146397</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>185419</t>
+          <t>184112</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -5733,12 +5733,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10700</t>
+          <t>10918</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5748,12 +5748,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11762</t>
+          <t>12467</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>7588</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19177</t>
+          <t>19602</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5846,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32616</t>
+          <t>31603</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50022</t>
+          <t>51131</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41588</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63155</t>
+          <t>63145</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>78513</t>
+          <t>78736</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106580</t>
+          <t>106575</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5959,12 +5959,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45219</t>
+          <t>44669</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65301</t>
+          <t>63574</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5974,12 +5974,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53213</t>
+          <t>53516</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75285</t>
+          <t>75122</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6009,12 +6009,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101023</t>
+          <t>103082</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>131181</t>
+          <t>133467</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>37,17%</t>
         </is>
       </c>
     </row>
@@ -6072,12 +6072,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35792</t>
+          <t>35674</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>54317</t>
+          <t>54464</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30073</t>
+          <t>31758</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>48675</t>
+          <t>49820</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6142,12 +6142,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>71022</t>
+          <t>71829</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>97295</t>
+          <t>98202</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25498</t>
+          <t>25535</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10990</t>
+          <t>10932</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23744</t>
+          <t>23324</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25854</t>
+          <t>25614</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43255</t>
+          <t>43210</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -6298,12 +6298,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4497</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14500</t>
+          <t>13580</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6333,12 +6333,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16160</t>
+          <t>16153</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>11622</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25505</t>
+          <t>25312</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -6528,12 +6528,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13028</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12421</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6598,12 +6598,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>9769</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>22486</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -6641,12 +6641,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60915</t>
+          <t>60459</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>86303</t>
+          <t>86938</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>80108</t>
+          <t>78152</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>109800</t>
+          <t>108435</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6711,12 +6711,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>147568</t>
+          <t>145951</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>187764</t>
+          <t>185976</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -6754,12 +6754,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>137824</t>
+          <t>136679</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>173347</t>
+          <t>173983</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6789,12 +6789,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>130992</t>
+          <t>132477</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>168051</t>
+          <t>166536</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6824,12 +6824,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>280353</t>
+          <t>278243</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>331754</t>
+          <t>327684</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>180292</t>
+          <t>180552</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>218531</t>
+          <t>217622</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6882,12 +6882,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>179120</t>
+          <t>181088</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>220435</t>
+          <t>221008</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>368336</t>
+          <t>369390</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>426658</t>
+          <t>426279</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -6980,12 +6980,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>129042</t>
+          <t>128015</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>162580</t>
+          <t>161532</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6995,12 +6995,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>155211</t>
+          <t>156139</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>194400</t>
+          <t>193412</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>294078</t>
+          <t>294173</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>345331</t>
+          <t>344930</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100496</t>
+          <t>101180</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>130854</t>
+          <t>133191</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>97531</t>
+          <t>97817</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>131330</t>
+          <t>132377</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7143,47 +7143,47 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
+          <t>17,92%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>230757</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>207773</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>254953</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>16,1%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>14,49%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
           <t>17,78%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>230757</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>206734</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>253923</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>16,1%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>14,42%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según como llegan a fin de mes con los ingresos de su hogar en 2023 (tasa de respuesta: 99,57%)</t>
+          <t>Adultos según como llegan a fin de mes con los ingresos de su hogar en 2023 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7667,12 +7667,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8851</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7682,12 +7682,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14654</t>
+          <t>14533</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>18821</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -7780,12 +7780,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19055</t>
+          <t>19158</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7795,12 +7795,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7815,12 +7815,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14365</t>
+          <t>14117</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12386</t>
+          <t>12754</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28651</t>
+          <t>29872</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -7893,12 +7893,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12801</t>
+          <t>11720</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31657</t>
+          <t>30178</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7928,12 +7928,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16851</t>
+          <t>17390</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31172</t>
+          <t>30680</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7963,12 +7963,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32891</t>
+          <t>32470</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55801</t>
+          <t>55711</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,35%</t>
         </is>
       </c>
     </row>
@@ -8006,12 +8006,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21084</t>
+          <t>21392</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8021,12 +8021,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8041,12 +8041,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8350</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18904</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17407</t>
+          <t>16919</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35804</t>
+          <t>35948</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -8119,12 +8119,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10883</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12917</t>
+          <t>13054</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>20212</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>2862</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11468</t>
+          <t>10882</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8364,12 +8364,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8419,12 +8419,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11434</t>
+          <t>11036</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -8462,12 +8462,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47098</t>
+          <t>47562</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75015</t>
+          <t>75392</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58620</t>
+          <t>58565</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>91043</t>
+          <t>89095</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>113236</t>
+          <t>113386</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>155244</t>
+          <t>155460</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98083</t>
+          <t>97654</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>142522</t>
+          <t>143462</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8610,12 +8610,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>134739</t>
+          <t>135356</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>176261</t>
+          <t>176466</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>247850</t>
+          <t>250978</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>310247</t>
+          <t>309381</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -8688,12 +8688,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>129653</t>
+          <t>127303</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177893</t>
+          <t>177100</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8703,12 +8703,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>172428</t>
+          <t>171532</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>225006</t>
+          <t>224011</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>311697</t>
+          <t>318879</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>386617</t>
+          <t>389086</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>41,14%</t>
         </is>
       </c>
     </row>
@@ -8801,12 +8801,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46081</t>
+          <t>46710</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>140712</t>
+          <t>145644</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8816,12 +8816,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>47679</t>
+          <t>48093</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73910</t>
+          <t>75146</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8851,12 +8851,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8871,12 +8871,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>104519</t>
+          <t>104493</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>217546</t>
+          <t>211049</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -8914,12 +8914,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12661</t>
+          <t>12785</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26884</t>
+          <t>26542</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8929,12 +8929,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12337</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30148</t>
+          <t>28415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8984,12 +8984,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28398</t>
+          <t>28420</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50581</t>
+          <t>50603</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10874</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15649</t>
+          <t>16061</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -9257,12 +9257,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57038</t>
+          <t>55397</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75309</t>
+          <t>75085</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9272,12 +9272,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58793</t>
+          <t>57792</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82918</t>
+          <t>83901</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9307,12 +9307,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>121028</t>
+          <t>121542</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>152474</t>
+          <t>151637</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>45,93%</t>
         </is>
       </c>
     </row>
@@ -9370,12 +9370,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48553</t>
+          <t>48848</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68383</t>
+          <t>67758</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9385,12 +9385,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71736</t>
+          <t>71173</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>96646</t>
+          <t>96756</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9420,12 +9420,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9440,12 +9440,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>125031</t>
+          <t>125858</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>156199</t>
+          <t>157720</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9455,12 +9455,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,77%</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9483,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10451</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24006</t>
+          <t>25247</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>11035</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27411</t>
+          <t>26088</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9533,12 +9533,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>25954</t>
+          <t>26236</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>45611</t>
+          <t>46652</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -9596,12 +9596,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>790</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>741</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9681,12 +9681,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -9714,7 +9714,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>709</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>8866</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -9939,12 +9939,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16366</t>
+          <t>16590</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9974,12 +9974,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10844</t>
+          <t>10480</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9989,12 +9989,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9454</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22525</t>
+          <t>22687</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -10052,12 +10052,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>108781</t>
+          <t>111944</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>149696</t>
+          <t>150227</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10087,12 +10087,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>131114</t>
+          <t>130506</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>171846</t>
+          <t>173634</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10102,12 +10102,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>254183</t>
+          <t>250516</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>312705</t>
+          <t>309513</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -10165,12 +10165,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>164418</t>
+          <t>165898</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>217003</t>
+          <t>216386</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>221614</t>
+          <t>224872</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>273590</t>
+          <t>273839</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10215,12 +10215,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>401717</t>
+          <t>403188</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>476097</t>
+          <t>478250</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -10278,12 +10278,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>162374</t>
+          <t>165908</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>216003</t>
+          <t>218261</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10293,12 +10293,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>210580</t>
+          <t>210854</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>268754</t>
+          <t>267771</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10328,12 +10328,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10348,12 +10348,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>390372</t>
+          <t>394597</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>472528</t>
+          <t>472332</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10363,12 +10363,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>59546</t>
+          <t>59710</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>182741</t>
+          <t>170062</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>62414</t>
+          <t>61765</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>91767</t>
+          <t>91154</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>133403</t>
+          <t>134088</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>251288</t>
+          <t>269245</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10476,12 +10476,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -10504,12 +10504,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18087</t>
+          <t>18164</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>35241</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20120</t>
+          <t>20335</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>40344</t>
+          <t>41444</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10574,12 +10574,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>42160</t>
+          <t>42998</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>70139</t>
+          <t>69305</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10589,12 +10589,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
